--- a/kawasaki_project/05_試算・管理シート/川崎町_新推計パターン_設定値一式_R8.9.11.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_新推計パターン_設定値一式_R8.9.11.xlsx
@@ -4176,9 +4176,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>【1】所得段階別第1号被保険者数（標準段階区分）　★第10〜13段階が0人のままです</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>【1】所得段階別第1号被保険者数（標準段階区分）　★令和7年度末の実績（年報）を反映しました</t>
         </is>
       </c>
     </row>
@@ -4215,16 +4215,20 @@
           <t>第1段階</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>449</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>448</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>447</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="B5" s="17" t="n">
+        <v>382</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>379</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>376</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>乗率 0.455　令和7年度末実績 383人（構成比 11.8％）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4232,16 +4236,20 @@
           <t>第2段階</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="B6" s="17" t="n">
+        <v>297</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>295</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>292</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>乗率 0.685　令和7年度末実績 298人（構成比 9.2％）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4249,16 +4257,20 @@
           <t>第3段階</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="17" t="n">
         <v>304</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="17" t="n">
+        <v>301</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>299</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>乗率 0.690　令和7年度末実績 305人（構成比 9.4％）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4266,16 +4278,20 @@
           <t>第4段階</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>394</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="B8" s="17" t="n">
+        <v>342</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>339</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>336</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>乗率 0.900　令和7年度末実績 343人（構成比 10.6％）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4283,16 +4299,20 @@
           <t>第5段階</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="17" t="n">
+        <v>677</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>671</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>666</v>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>651</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>637</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>乗率 1.000　令和7年度末実績 679人（構成比 21.0％）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4300,16 +4320,20 @@
           <t>第6段階</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>448</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>446</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>443</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="B10" s="17" t="n">
+        <v>409</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>405</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>402</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>乗率 1.200　令和7年度末実績 410人（構成比 12.7％）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4317,16 +4341,20 @@
           <t>第7段階</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>382</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="B11" s="17" t="n">
+        <v>426</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>422</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>419</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>乗率 1.300　令和7年度末実績 427人（構成比 13.2％）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4334,16 +4362,20 @@
           <t>第8段階</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>193</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="B12" s="17" t="n">
+        <v>231</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>229</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>227</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>乗率 1.500　令和7年度末実績 232人（構成比 7.2％）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4351,18 +4383,18 @@
           <t>第9段階</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>80</v>
+      <c r="C13" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>83</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>現在ここで頭打ちになっています</t>
+          <t>乗率 1.700　令和7年度末実績 85人（構成比 2.6％）</t>
         </is>
       </c>
     </row>
@@ -4372,18 +4404,18 @@
           <t>第10段階</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
+      <c r="B14" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>26</v>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>★要入力</t>
+          <t>乗率 1.900　令和7年度末実績 26人（構成比 0.8％）</t>
         </is>
       </c>
     </row>
@@ -4393,18 +4425,18 @@
           <t>第11段階</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>0</v>
+      <c r="B15" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>17</v>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>★要入力</t>
+          <t>乗率 2.100　令和7年度末実績 17人（構成比 0.5％）</t>
         </is>
       </c>
     </row>
@@ -4414,18 +4446,18 @@
           <t>第12段階</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0</v>
+      <c r="B16" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>★要入力</t>
+          <t>乗率 2.300　令和7年度末実績 7人（構成比 0.2％）</t>
         </is>
       </c>
     </row>
@@ -4435,18 +4467,18 @@
           <t>第13段階</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>0</v>
+      <c r="B17" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>27</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>★要入力</t>
+          <t>乗率 2.400　令和7年度末実績 28人（構成比 0.9％）</t>
         </is>
       </c>
     </row>
@@ -4470,21 +4502,21 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>※ 令和7年度（または令和8年度）の所得段階別第1号被保険者数の実績（13段階）をご用意ください。</t>
+          <t>※ 出所：介護保険事業状況報告（年報・令和7年度）様式1「所得段階別」列20「年度末現在被保険者数」。令和7年度末の実績構成比を各年度の第1号被保険者数見込みに割り付けています。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 現在は第9段階で頭打ちになっており、本来その一部が第10〜13段階に分かれます。</t>
+          <t xml:space="preserve">　 これまで第9段階で頭打ち（第10〜13段階が0人）になっていたため、所得段階別加入割合による補正係数が 0.964047 と低く出ていました。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 第10〜13段階は基準額に対する割合が1.9〜2.4倍と高いため、入力すると保険料基準額は月額238〜350円下がります。</t>
+          <t xml:space="preserve">　 実績を反映すると補正係数は 1.013748 となり、保険料基準額は月額352円下がります（取崩なしで6,822円）。</t>
         </is>
       </c>
     </row>
